--- a/data/processed/harmonization/Acidity__Soil_pH/dois_filtering.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/dois_filtering.xlsx
@@ -2012,7 +2012,7 @@
         <v>126</v>
       </c>
       <c r="D48">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E48" t="s">
         <v>197</v>
@@ -2072,7 +2072,7 @@
         <v>126</v>
       </c>
       <c r="D51">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="E51" t="s">
         <v>200</v>
